--- a/Processos_de_Fabricacao.xlsx
+++ b/Processos_de_Fabricacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orcamento\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFCE423-83F5-42B9-917C-ABFAFF19A32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75217335-9A90-4D0B-85E6-79BA23CEFDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Processos" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Processos!$A$1:$AB$741</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2740,14 +2753,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF33645A-C41E-42FF-8EC5-04EEB9194698}">
   <dimension ref="A1:AA626"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>80</v>
       </c>
@@ -2830,7 +2843,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2850,7 +2863,7 @@
         <v>108</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2911,10 +2924,10 @@
       </c>
       <c r="AA2" s="7">
         <f>SUM(G2:Z2)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2998,7 +3011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3082,7 +3095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3166,7 +3179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3250,7 +3263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3334,7 +3347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3418,7 +3431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3502,7 +3515,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3586,7 +3599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3670,7 +3683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3754,7 +3767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3838,7 +3851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3922,7 +3935,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4006,7 +4019,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4090,7 +4103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -4174,7 +4187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4258,7 +4271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -4342,7 +4355,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -4426,7 +4439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -4510,7 +4523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -4594,7 +4607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -4678,7 +4691,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4762,7 +4775,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4846,7 +4859,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4930,7 +4943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -5014,7 +5027,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -5098,7 +5111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5182,7 +5195,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5266,7 +5279,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5350,7 +5363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5434,7 +5447,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5518,7 +5531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5602,7 +5615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5686,7 +5699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5770,7 +5783,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -5854,7 +5867,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -5938,7 +5951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -6022,7 +6035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -6106,7 +6119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -6190,7 +6203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -6274,7 +6287,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -6358,7 +6371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -6442,7 +6455,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -6526,7 +6539,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -6610,7 +6623,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -6694,7 +6707,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -6778,7 +6791,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -6862,7 +6875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6946,7 +6959,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -7030,7 +7043,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -7114,7 +7127,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -7198,7 +7211,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -7282,7 +7295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -7366,7 +7379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -7450,7 +7463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -7534,7 +7547,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -7618,7 +7631,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -7702,7 +7715,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -7786,7 +7799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -7870,7 +7883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -7954,7 +7967,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -8038,7 +8051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -8122,7 +8135,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -8206,7 +8219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -8290,7 +8303,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -8374,7 +8387,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -8458,7 +8471,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -8542,7 +8555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -8626,7 +8639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -8710,7 +8723,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -8794,7 +8807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -8878,7 +8891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -8962,7 +8975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -9046,7 +9059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -9130,7 +9143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -9214,7 +9227,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -9298,7 +9311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -9382,7 +9395,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -9466,7 +9479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -9550,7 +9563,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -9634,7 +9647,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -9718,7 +9731,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -9802,7 +9815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -9886,7 +9899,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -9970,7 +9983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -10054,7 +10067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -10138,7 +10151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -10222,7 +10235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -10306,7 +10319,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -10390,7 +10403,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -10474,7 +10487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -10558,7 +10571,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -10642,7 +10655,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -10726,7 +10739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -10810,7 +10823,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -10894,7 +10907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -10978,7 +10991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -11062,7 +11075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -11146,7 +11159,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -11230,7 +11243,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -11314,7 +11327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -11398,7 +11411,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -11482,7 +11495,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -11566,7 +11579,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -11650,7 +11663,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -11734,7 +11747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -11818,7 +11831,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -11902,7 +11915,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -11986,7 +11999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -12070,7 +12083,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -12154,7 +12167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -12238,7 +12251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -12322,7 +12335,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -12406,7 +12419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -12490,7 +12503,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -12574,7 +12587,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -12658,7 +12671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -12742,7 +12755,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -12826,7 +12839,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -12910,7 +12923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -12994,7 +13007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -13078,7 +13091,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -13162,7 +13175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -13246,7 +13259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -13330,7 +13343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -13414,7 +13427,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -13498,7 +13511,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -13582,7 +13595,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -13666,7 +13679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -13750,7 +13763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -13834,7 +13847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -13918,7 +13931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -14002,7 +14015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -14086,7 +14099,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -14170,7 +14183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -14254,7 +14267,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -14338,7 +14351,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -14422,7 +14435,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -14506,7 +14519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -14590,7 +14603,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -14674,7 +14687,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -14758,7 +14771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -14842,7 +14855,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -14926,7 +14939,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -15010,7 +15023,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -15094,7 +15107,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -15178,7 +15191,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -15262,7 +15275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -15346,7 +15359,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -15430,7 +15443,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -15514,7 +15527,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -15598,7 +15611,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -15682,7 +15695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -15766,7 +15779,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -15850,7 +15863,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -15934,7 +15947,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -16018,7 +16031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -16102,7 +16115,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -16186,7 +16199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -16270,7 +16283,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -16354,7 +16367,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -16438,7 +16451,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -16522,7 +16535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -16606,7 +16619,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -16690,7 +16703,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -16774,7 +16787,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -16856,7 +16869,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -16940,7 +16953,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -17024,7 +17037,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -17108,7 +17121,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -17192,7 +17205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -17276,7 +17289,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -17360,7 +17373,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -17444,7 +17457,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -17528,7 +17541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -17612,7 +17625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -17696,7 +17709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -17780,7 +17793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -17864,7 +17877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -17948,7 +17961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -18032,7 +18045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -18116,7 +18129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -18200,7 +18213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -18284,7 +18297,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -18368,7 +18381,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -18452,7 +18465,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -18536,7 +18549,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -18620,7 +18633,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -18704,7 +18717,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -18788,7 +18801,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -18872,7 +18885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -18956,7 +18969,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -19040,7 +19053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -19124,7 +19137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -19208,7 +19221,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -19292,7 +19305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -19376,7 +19389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -19460,7 +19473,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -19544,7 +19557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -19628,7 +19641,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -19712,7 +19725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -19796,7 +19809,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -19880,7 +19893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -19964,7 +19977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -20048,7 +20061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -20132,7 +20145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -20216,7 +20229,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -20300,7 +20313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -20384,7 +20397,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -20468,7 +20481,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -20552,7 +20565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -20636,7 +20649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -20720,7 +20733,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -20804,7 +20817,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -20888,7 +20901,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -20972,7 +20985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -21056,7 +21069,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -21140,7 +21153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -21224,7 +21237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -21308,7 +21321,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -21392,7 +21405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -21476,7 +21489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -21560,7 +21573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -21644,7 +21657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -21728,7 +21741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -21812,7 +21825,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -21896,7 +21909,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -21980,7 +21993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -22064,7 +22077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -22148,7 +22161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -22232,7 +22245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -22316,7 +22329,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -22400,7 +22413,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -22484,7 +22497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -22568,7 +22581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -22652,7 +22665,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -22736,7 +22749,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -22820,7 +22833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -22904,7 +22917,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -22988,7 +23001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -23072,7 +23085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -23156,7 +23169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -23240,7 +23253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -23324,7 +23337,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -23408,7 +23421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -23490,7 +23503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -23574,7 +23587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -23658,7 +23671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -23742,7 +23755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -23826,7 +23839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -23910,7 +23923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -23994,7 +24007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -24078,7 +24091,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -24162,7 +24175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -24246,7 +24259,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -24330,7 +24343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -24414,7 +24427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -24498,7 +24511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -24582,7 +24595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -24666,7 +24679,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>261</v>
       </c>
@@ -24750,7 +24763,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -24834,7 +24847,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -24918,7 +24931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -25002,7 +25015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -25086,7 +25099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -25170,7 +25183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -25254,7 +25267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -25338,7 +25351,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>269</v>
       </c>
@@ -25422,7 +25435,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -25506,7 +25519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>271</v>
       </c>
@@ -25590,7 +25603,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -25674,7 +25687,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -25758,7 +25771,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -25842,7 +25855,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -25926,7 +25939,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>276</v>
       </c>
@@ -26010,7 +26023,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -26094,7 +26107,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>278</v>
       </c>
@@ -26178,7 +26191,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -26262,7 +26275,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -26346,7 +26359,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -26430,7 +26443,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -26514,7 +26527,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -26598,7 +26611,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -26682,7 +26695,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -26766,7 +26779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -26850,7 +26863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -26934,7 +26947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>288</v>
       </c>
@@ -27018,7 +27031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -27102,7 +27115,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>290</v>
       </c>
@@ -27186,7 +27199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -27270,7 +27283,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -27354,7 +27367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -27438,7 +27451,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -27522,7 +27535,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -27606,7 +27619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -27690,7 +27703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -27774,7 +27787,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>298</v>
       </c>
@@ -27858,7 +27871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>299</v>
       </c>
@@ -27942,7 +27955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>300</v>
       </c>
@@ -28026,7 +28039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>301</v>
       </c>
@@ -28110,7 +28123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -28194,7 +28207,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>303</v>
       </c>
@@ -28278,7 +28291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>304</v>
       </c>
@@ -28362,7 +28375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>305</v>
       </c>
@@ -28446,7 +28459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>306</v>
       </c>
@@ -28530,7 +28543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>307</v>
       </c>
@@ -28614,7 +28627,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>308</v>
       </c>
@@ -28698,7 +28711,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>309</v>
       </c>
@@ -28782,7 +28795,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>310</v>
       </c>
@@ -28866,7 +28879,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>311</v>
       </c>
@@ -28950,7 +28963,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>312</v>
       </c>
@@ -29034,7 +29047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -29118,7 +29131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>314</v>
       </c>
@@ -29202,7 +29215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>315</v>
       </c>
@@ -29286,7 +29299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>316</v>
       </c>
@@ -29370,7 +29383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>317</v>
       </c>
@@ -29454,7 +29467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>318</v>
       </c>
@@ -29538,7 +29551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>319</v>
       </c>
@@ -29622,7 +29635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>320</v>
       </c>
@@ -29706,7 +29719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>321</v>
       </c>
@@ -29790,7 +29803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>322</v>
       </c>
@@ -29874,7 +29887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -29958,7 +29971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>324</v>
       </c>
@@ -30042,7 +30055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>325</v>
       </c>
@@ -30126,7 +30139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -30210,7 +30223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -30294,7 +30307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -30378,7 +30391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -30462,7 +30475,7 @@
         <v>13.613</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>330</v>
       </c>
@@ -30546,7 +30559,7 @@
         <v>10.148</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -30630,7 +30643,7 @@
         <v>23.009999999999998</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -30714,7 +30727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -30798,7 +30811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -30882,7 +30895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -30966,7 +30979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -31050,7 +31063,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>337</v>
       </c>
@@ -31134,7 +31147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -31218,7 +31231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>339</v>
       </c>
@@ -31302,7 +31315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>340</v>
       </c>
@@ -31386,7 +31399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>341</v>
       </c>
@@ -31470,7 +31483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>342</v>
       </c>
@@ -31554,7 +31567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -31638,7 +31651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>344</v>
       </c>
@@ -31722,7 +31735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>345</v>
       </c>
@@ -31806,7 +31819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>346</v>
       </c>
@@ -31890,7 +31903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>347</v>
       </c>
@@ -31974,7 +31987,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -32058,7 +32071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>349</v>
       </c>
@@ -32142,7 +32155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>350</v>
       </c>
@@ -32226,7 +32239,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>351</v>
       </c>
@@ -32310,7 +32323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>352</v>
       </c>
@@ -32394,7 +32407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>353</v>
       </c>
@@ -32478,7 +32491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -32562,7 +32575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>355</v>
       </c>
@@ -32646,7 +32659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>356</v>
       </c>
@@ -32730,7 +32743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>357</v>
       </c>
@@ -32814,7 +32827,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>358</v>
       </c>
@@ -32898,7 +32911,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -32982,7 +32995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>360</v>
       </c>
@@ -33066,7 +33079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>361</v>
       </c>
@@ -33150,7 +33163,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -33234,7 +33247,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>363</v>
       </c>
@@ -33318,7 +33331,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -33402,7 +33415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>365</v>
       </c>
@@ -33486,7 +33499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>366</v>
       </c>
@@ -33570,7 +33583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>367</v>
       </c>
@@ -33654,7 +33667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>368</v>
       </c>
@@ -33738,7 +33751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -33822,7 +33835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>370</v>
       </c>
@@ -33906,7 +33919,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -33990,7 +34003,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>372</v>
       </c>
@@ -34074,7 +34087,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>373</v>
       </c>
@@ -34158,7 +34171,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>374</v>
       </c>
@@ -34242,7 +34255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>375</v>
       </c>
@@ -34326,7 +34339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>376</v>
       </c>
@@ -34410,7 +34423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>377</v>
       </c>
@@ -34494,7 +34507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>378</v>
       </c>
@@ -34578,7 +34591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>379</v>
       </c>
@@ -34662,7 +34675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>380</v>
       </c>
@@ -34746,7 +34759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>381</v>
       </c>
@@ -34830,7 +34843,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>382</v>
       </c>
@@ -34914,7 +34927,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>383</v>
       </c>
@@ -34998,7 +35011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -35082,7 +35095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="386" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>385</v>
       </c>
@@ -35166,7 +35179,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="387" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>386</v>
       </c>
@@ -35250,7 +35263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="388" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>387</v>
       </c>
@@ -35334,7 +35347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="389" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>388</v>
       </c>
@@ -35418,7 +35431,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="390" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -35502,7 +35515,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="391" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>390</v>
       </c>
@@ -35586,7 +35599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="392" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>391</v>
       </c>
@@ -35670,7 +35683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>392</v>
       </c>
@@ -35754,7 +35767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>393</v>
       </c>
@@ -35838,7 +35851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="395" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>394</v>
       </c>
@@ -35922,7 +35935,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="396" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>395</v>
       </c>
@@ -36006,7 +36019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="397" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>396</v>
       </c>
@@ -36090,7 +36103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="398" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>397</v>
       </c>
@@ -36174,7 +36187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="399" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>398</v>
       </c>
@@ -36258,7 +36271,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="400" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>399</v>
       </c>
@@ -36342,7 +36355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="401" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>400</v>
       </c>
@@ -36426,7 +36439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="402" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>401</v>
       </c>
@@ -36510,7 +36523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="403" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>402</v>
       </c>
@@ -36594,7 +36607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="404" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -36678,7 +36691,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="405" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>404</v>
       </c>
@@ -36762,7 +36775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>405</v>
       </c>
@@ -36846,7 +36859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="407" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>406</v>
       </c>
@@ -36930,7 +36943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="408" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>407</v>
       </c>
@@ -37014,7 +37027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="409" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>408</v>
       </c>
@@ -37098,7 +37111,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="410" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>409</v>
       </c>
@@ -37182,7 +37195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="411" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>410</v>
       </c>
@@ -37266,7 +37279,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="412" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>411</v>
       </c>
@@ -37350,7 +37363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="413" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>412</v>
       </c>
@@ -37434,7 +37447,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="414" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>413</v>
       </c>
@@ -37518,7 +37531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="415" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>414</v>
       </c>
@@ -37602,7 +37615,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="416" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>415</v>
       </c>
@@ -37686,7 +37699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="417" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>416</v>
       </c>
@@ -37770,7 +37783,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="418" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>417</v>
       </c>
@@ -37854,7 +37867,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="419" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>418</v>
       </c>
@@ -37938,7 +37951,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="420" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>419</v>
       </c>
@@ -38022,7 +38035,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="421" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>420</v>
       </c>
@@ -38106,7 +38119,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="422" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>421</v>
       </c>
@@ -38190,7 +38203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="423" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>422</v>
       </c>
@@ -38274,7 +38287,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="424" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>423</v>
       </c>
@@ -38358,7 +38371,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="425" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>424</v>
       </c>
@@ -38442,7 +38455,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="426" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>425</v>
       </c>
@@ -38526,7 +38539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>426</v>
       </c>
@@ -38610,7 +38623,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="428" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>427</v>
       </c>
@@ -38694,7 +38707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="429" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>428</v>
       </c>
@@ -38778,7 +38791,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="430" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>429</v>
       </c>
@@ -38862,7 +38875,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="431" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>430</v>
       </c>
@@ -38946,7 +38959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>431</v>
       </c>
@@ -39030,7 +39043,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="433" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>432</v>
       </c>
@@ -39114,7 +39127,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="434" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>433</v>
       </c>
@@ -39198,7 +39211,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="435" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>434</v>
       </c>
@@ -39282,7 +39295,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="436" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>435</v>
       </c>
@@ -39366,7 +39379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="437" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>436</v>
       </c>
@@ -39450,7 +39463,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="438" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>437</v>
       </c>
@@ -39534,7 +39547,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="439" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>438</v>
       </c>
@@ -39618,7 +39631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="440" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>439</v>
       </c>
@@ -39702,7 +39715,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="441" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>440</v>
       </c>
@@ -39786,7 +39799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="442" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>441</v>
       </c>
@@ -39870,7 +39883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="443" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>442</v>
       </c>
@@ -39954,7 +39967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>443</v>
       </c>
@@ -40038,7 +40051,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>444</v>
       </c>
@@ -40122,7 +40135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="446" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>445</v>
       </c>
@@ -40206,7 +40219,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="447" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>446</v>
       </c>
@@ -40290,7 +40303,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="448" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>447</v>
       </c>
@@ -40374,7 +40387,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="449" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>448</v>
       </c>
@@ -40458,7 +40471,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="450" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>449</v>
       </c>
@@ -40542,7 +40555,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="451" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>450</v>
       </c>
@@ -40626,7 +40639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>451</v>
       </c>
@@ -40710,7 +40723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="453" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>452</v>
       </c>
@@ -40794,7 +40807,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="454" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>453</v>
       </c>
@@ -40878,7 +40891,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="455" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>454</v>
       </c>
@@ -40962,7 +40975,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="456" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>455</v>
       </c>
@@ -41046,7 +41059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="457" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>456</v>
       </c>
@@ -41130,7 +41143,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="458" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>457</v>
       </c>
@@ -41214,7 +41227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="459" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>458</v>
       </c>
@@ -41298,7 +41311,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="460" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>459</v>
       </c>
@@ -41382,7 +41395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="461" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>460</v>
       </c>
@@ -41466,7 +41479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="462" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>461</v>
       </c>
@@ -41550,7 +41563,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="463" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>462</v>
       </c>
@@ -41634,7 +41647,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="464" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>463</v>
       </c>
@@ -41718,7 +41731,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="465" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>464</v>
       </c>
@@ -41802,7 +41815,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="466" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>465</v>
       </c>
@@ -41886,7 +41899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>466</v>
       </c>
@@ -41970,7 +41983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="468" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>467</v>
       </c>
@@ -42054,7 +42067,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="469" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>468</v>
       </c>
@@ -42138,7 +42151,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="470" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>469</v>
       </c>
@@ -42222,7 +42235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="471" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>470</v>
       </c>
@@ -42306,7 +42319,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="472" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>471</v>
       </c>
@@ -42390,7 +42403,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="473" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>472</v>
       </c>
@@ -42474,7 +42487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="474" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>473</v>
       </c>
@@ -42558,7 +42571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="475" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>474</v>
       </c>
@@ -42642,7 +42655,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="476" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>475</v>
       </c>
@@ -42726,7 +42739,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="477" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>476</v>
       </c>
@@ -42810,7 +42823,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="478" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>477</v>
       </c>
@@ -42894,7 +42907,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="479" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>478</v>
       </c>
@@ -42978,7 +42991,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="480" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>479</v>
       </c>
@@ -43062,7 +43075,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="481" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>480</v>
       </c>
@@ -43146,7 +43159,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="482" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>481</v>
       </c>
@@ -43230,7 +43243,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="483" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>482</v>
       </c>
@@ -43314,7 +43327,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="484" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>483</v>
       </c>
@@ -43398,7 +43411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="485" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>484</v>
       </c>
@@ -43480,7 +43493,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="486" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>485</v>
       </c>
@@ -43564,7 +43577,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="487" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>486</v>
       </c>
@@ -43648,7 +43661,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="488" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>487</v>
       </c>
@@ -43732,7 +43745,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="489" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>488</v>
       </c>
@@ -43816,7 +43829,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>489</v>
       </c>
@@ -43900,7 +43913,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="491" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>490</v>
       </c>
@@ -43984,7 +43997,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="492" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>491</v>
       </c>
@@ -44068,7 +44081,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="493" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>492</v>
       </c>
@@ -44152,7 +44165,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="494" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>493</v>
       </c>
@@ -44236,7 +44249,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="495" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>494</v>
       </c>
@@ -44320,7 +44333,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="496" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>495</v>
       </c>
@@ -44404,7 +44417,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="497" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>496</v>
       </c>
@@ -44488,7 +44501,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="498" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>497</v>
       </c>
@@ -44572,7 +44585,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="499" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>498</v>
       </c>
@@ -44656,7 +44669,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="500" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>499</v>
       </c>
@@ -44738,7 +44751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="501" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>500</v>
       </c>
@@ -44822,7 +44835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="502" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>501</v>
       </c>
@@ -44906,7 +44919,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="503" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>502</v>
       </c>
@@ -44990,7 +45003,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="504" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>503</v>
       </c>
@@ -45074,7 +45087,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="505" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>504</v>
       </c>
@@ -45158,7 +45171,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="506" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>505</v>
       </c>
@@ -45242,7 +45255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>506</v>
       </c>
@@ -45326,7 +45339,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="508" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>507</v>
       </c>
@@ -45410,7 +45423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="509" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>508</v>
       </c>
@@ -45494,7 +45507,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="510" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>509</v>
       </c>
@@ -45578,7 +45591,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="511" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>510</v>
       </c>
@@ -45662,7 +45675,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="512" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>511</v>
       </c>
@@ -45746,7 +45759,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="513" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>512</v>
       </c>
@@ -45830,7 +45843,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="514" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>513</v>
       </c>
@@ -45912,7 +45925,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="515" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>514</v>
       </c>
@@ -45994,7 +46007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="516" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>515</v>
       </c>
@@ -46078,7 +46091,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="517" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>516</v>
       </c>
@@ -46162,7 +46175,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="518" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>517</v>
       </c>
@@ -46246,7 +46259,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="519" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>518</v>
       </c>
@@ -46330,7 +46343,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="520" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>519</v>
       </c>
@@ -46414,7 +46427,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="521" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>520</v>
       </c>
@@ -46498,7 +46511,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="522" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>521</v>
       </c>
@@ -46582,7 +46595,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="523" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>522</v>
       </c>
@@ -46666,7 +46679,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="524" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>523</v>
       </c>
@@ -46750,7 +46763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="525" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>524</v>
       </c>
@@ -46834,7 +46847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="526" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>525</v>
       </c>
@@ -46918,7 +46931,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="527" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>526</v>
       </c>
@@ -47002,7 +47015,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="528" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>527</v>
       </c>
@@ -47086,7 +47099,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="529" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>528</v>
       </c>
@@ -47170,7 +47183,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="530" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>529</v>
       </c>
@@ -47254,7 +47267,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="531" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>530</v>
       </c>
@@ -47338,7 +47351,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="532" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>531</v>
       </c>
@@ -47420,7 +47433,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="533" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>532</v>
       </c>
@@ -47504,7 +47517,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="534" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>533</v>
       </c>
@@ -47588,7 +47601,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="535" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>534</v>
       </c>
@@ -47672,7 +47685,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="536" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>535</v>
       </c>
@@ -47756,7 +47769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="537" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>536</v>
       </c>
@@ -47840,7 +47853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="538" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>537</v>
       </c>
@@ -47924,7 +47937,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="539" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>538</v>
       </c>
@@ -48008,7 +48021,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="540" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>539</v>
       </c>
@@ -48092,7 +48105,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="541" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>540</v>
       </c>
@@ -48176,7 +48189,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="542" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>541</v>
       </c>
@@ -48260,7 +48273,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="543" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>542</v>
       </c>
@@ -48344,7 +48357,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="544" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>543</v>
       </c>
@@ -48428,7 +48441,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="545" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>544</v>
       </c>
@@ -48512,7 +48525,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="546" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>545</v>
       </c>
@@ -48596,7 +48609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="547" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>546</v>
       </c>
@@ -48680,7 +48693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="548" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>547</v>
       </c>
@@ -48764,7 +48777,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="549" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>548</v>
       </c>
@@ -48848,7 +48861,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="550" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>549</v>
       </c>
@@ -48932,7 +48945,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="551" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>550</v>
       </c>
@@ -49016,7 +49029,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="552" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>551</v>
       </c>
@@ -49100,7 +49113,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="553" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>552</v>
       </c>
@@ -49184,7 +49197,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="554" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>553</v>
       </c>
@@ -49268,7 +49281,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="555" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>554</v>
       </c>
@@ -49352,7 +49365,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="556" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>555</v>
       </c>
@@ -49436,7 +49449,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="557" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>556</v>
       </c>
@@ -49520,7 +49533,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="558" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>557</v>
       </c>
@@ -49604,7 +49617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="559" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>558</v>
       </c>
@@ -49688,7 +49701,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="560" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>559</v>
       </c>
@@ -49772,7 +49785,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="561" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>560</v>
       </c>
@@ -49856,7 +49869,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="562" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>561</v>
       </c>
@@ -49940,7 +49953,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="563" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>562</v>
       </c>
@@ -50024,7 +50037,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="564" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>563</v>
       </c>
@@ -50108,7 +50121,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="565" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>564</v>
       </c>
@@ -50192,7 +50205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>565</v>
       </c>
@@ -50276,7 +50289,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="567" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>566</v>
       </c>
@@ -50360,7 +50373,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="568" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>567</v>
       </c>
@@ -50444,7 +50457,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="569" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>568</v>
       </c>
@@ -50528,7 +50541,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="570" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>569</v>
       </c>
@@ -50612,7 +50625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="571" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>570</v>
       </c>
@@ -50696,7 +50709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="572" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>571</v>
       </c>
@@ -50780,7 +50793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="573" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>572</v>
       </c>
@@ -50864,7 +50877,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="574" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>573</v>
       </c>
@@ -50948,7 +50961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="575" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>574</v>
       </c>
@@ -51032,7 +51045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="576" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>575</v>
       </c>
@@ -51116,7 +51129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="577" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>576</v>
       </c>
@@ -51200,7 +51213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="578" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>577</v>
       </c>
@@ -51284,7 +51297,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="579" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>578</v>
       </c>
@@ -51368,7 +51381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="580" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>579</v>
       </c>
@@ -51452,7 +51465,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="581" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>580</v>
       </c>
@@ -51536,7 +51549,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="582" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>581</v>
       </c>
@@ -51620,7 +51633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="583" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>582</v>
       </c>
@@ -51704,7 +51717,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="584" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>583</v>
       </c>
@@ -51788,7 +51801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>584</v>
       </c>
@@ -51872,7 +51885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>585</v>
       </c>
@@ -51956,7 +51969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="587" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>586</v>
       </c>
@@ -52040,7 +52053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>587</v>
       </c>
@@ -52124,7 +52137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>588</v>
       </c>
@@ -52208,7 +52221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="590" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>589</v>
       </c>
@@ -52292,7 +52305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>590</v>
       </c>
@@ -52376,7 +52389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="592" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>591</v>
       </c>
@@ -52460,7 +52473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>592</v>
       </c>
@@ -52544,7 +52557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>593</v>
       </c>
@@ -52628,7 +52641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>594</v>
       </c>
@@ -52712,7 +52725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="596" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>595</v>
       </c>
@@ -52796,7 +52809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="597" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>596</v>
       </c>
@@ -52880,7 +52893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="598" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>597</v>
       </c>
@@ -52964,7 +52977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>598</v>
       </c>
@@ -53048,7 +53061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>599</v>
       </c>
@@ -53132,7 +53145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>600</v>
       </c>
@@ -53216,7 +53229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>601</v>
       </c>
@@ -53300,7 +53313,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="603" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>602</v>
       </c>
@@ -53384,7 +53397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>603</v>
       </c>
@@ -53468,7 +53481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>604</v>
       </c>
@@ -53552,7 +53565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>605</v>
       </c>
@@ -53636,7 +53649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>606</v>
       </c>
@@ -53720,7 +53733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>607</v>
       </c>
@@ -53804,7 +53817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>608</v>
       </c>
@@ -53888,7 +53901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>609</v>
       </c>
@@ -53972,7 +53985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>610</v>
       </c>
@@ -54054,7 +54067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>611</v>
       </c>
@@ -54138,7 +54151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="613" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>612</v>
       </c>
@@ -54222,7 +54235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="614" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>613</v>
       </c>
@@ -54306,7 +54319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="615" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>614</v>
       </c>
@@ -54390,7 +54403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="616" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>615</v>
       </c>
@@ -54474,7 +54487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="617" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>616</v>
       </c>
@@ -54558,7 +54571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="618" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>617</v>
       </c>
@@ -54642,7 +54655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="619" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>618</v>
       </c>
@@ -54726,7 +54739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="620" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>619</v>
       </c>
@@ -54810,7 +54823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="621" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>620</v>
       </c>
@@ -54892,7 +54905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="622" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>621</v>
       </c>
@@ -54974,7 +54987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="623" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>622</v>
       </c>
@@ -55056,7 +55069,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="624" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>623</v>
       </c>
@@ -55138,7 +55151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>624</v>
       </c>
@@ -55220,7 +55233,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="626" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>625</v>
       </c>

--- a/Processos_de_Fabricacao.xlsx
+++ b/Processos_de_Fabricacao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Downloads\aps-producao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429F3660-0FC5-4DF8-988A-EBAF36B6EB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423EC461-262D-4769-BFF2-B5092A78593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Processos" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Processos!$A$1:$X$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Processos!$A$1:$X$625</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43562,7 +43562,7 @@
         <v>0</v>
       </c>
       <c r="W578" s="5">
-        <f t="shared" ref="W578:W641" si="9">SUM(C578:V578)</f>
+        <f t="shared" ref="W578:W625" si="9">SUM(C578:V578)</f>
         <v>25</v>
       </c>
     </row>
@@ -46951,7 +46951,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X379" xr:uid="{AF33645A-C41E-42FF-8EC5-04EEB9194698}">
+  <autoFilter ref="A1:X625" xr:uid="{AF33645A-C41E-42FF-8EC5-04EEB9194698}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W721">
       <sortCondition ref="B1:B379"/>
     </sortState>
